--- a/fintech_companies_structured.xlsx
+++ b/fintech_companies_structured.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.grab.careers/en/jobs/</t>
+          <t>https://www.pinelabs.com/careers/</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://tickets.paytm.com/trains/</t>
+          <t>https://paytm.com/careers/</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.freshersworld.com/jobs/human-resources-hr-jobs-in-across-india-bharatpe-1451827</t>
+          <t>https://www.bharatpe.com/careers/</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.careermine.com/jobs/</t>
+          <t>https://careers.cred.club/openings</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.careermine.com/jobs/</t>
+          <t>https://careers.zerodha.com/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://jobsforcommerce.com/category/all-india-job/page/3/</t>
+          <t>https://www.groww.in/careers/</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://jobs4fresher.com/upstox-off-campus-recruitment-oct-2023/</t>
+          <t>https://www.upstox.com/careers/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://policybazaar.hire.trakstar.com/jobs</t>
+          <t>https://www.policybazaar.com/careers/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.freshersworld.com/jobs/operations-sports-sponsorship-jobs-in-across-india-acko-general-insurance-1434913</t>
+          <t>https://www.acko.com/careers/</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.ambitionbox.com/jobs/digit-insurance-jobs-cmp</t>
+          <t>https://www.godigit.com/careers/</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://internshala.com/jobs/job-at-turtlemint/</t>
+          <t>https://careers.turtlemint.com/</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.ambitionbox.com/jobs/paisabazaar-dot-com-jobs-cmp</t>
+          <t>https://www.paisabazaar.com/careers/</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://builtintoronto.com/company/cash-app/jobs</t>
+          <t>https://www.cashe.co.in/careers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.grab.careers/en/jobs/</t>
+          <t>https://www.lazypay.in/careers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://cutshort.io/company/jobs-at-simprosys-infomedia-18-p3ps0pga</t>
+          <t>https://www.getsimpl.com/careers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.zhihu.com/question/615604129</t>
+          <t>https://careers.uni.cards/</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://cutshort.io/company/onecard-25-mLS1R9Z2</t>
+          <t>https://www.getonecard.app/careers/</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.shine.com/job-search/jobs-in-Navi</t>
+          <t>https://www.navi.com/careers/</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://careers.unilever.com/</t>
+          <t>https://www.fi.money/careers/</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://uchilife.actlever.co.jp/pulsepremiere/</t>
+          <t>https://www.razorpay.com/careers/</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.grab.careers/en/jobs/</t>
+          <t>https://www.billdesk.com/careers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://www.kitjob.in/job/247549657/assistant-manager-key-accounts-management-ccavenue-india</t>
+          <t>https://careers.ccavenue.com/</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://www.freshersworld.com/jobs/business-development-sales-jobs-in-across-india-mobikwik-1255877</t>
+          <t>https://www.mobikwik.com/careers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://www.ambitionbox.com/overview/paynearby-technologies-overview</t>
+          <t>https://www.paynearby.in/careers/</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://www.instahyre.com/jobs-at-ezetap/</t>
+          <t>https://www.ezetap.com/careers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/fampay/jobs/N4ojybAAB-india-fampay-site-reliability-engineer</t>
+          <t>https://jobs.lever.co/fampay</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://www.grab.careers/en/jobs/</t>
+          <t>https://www.axio.co.in/careers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://www.airtribe.live/jobs/companies/indmoney--A9I0RM8TV51T</t>
+          <t>https://www.indmoney.com/careers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://www.instahyre.com/jobs-at-kuvera/</t>
+          <t>https://www.kuverapartners.com/careers/</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://nextleap.app/jobs/data-analyst/business-analyst-smallcase/jvhrzoou</t>
+          <t>https://careers.smallcase.com/</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://confluencr.com/tickertape-case-study/</t>
+          <t>https://www.tickertape.in/careers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://wellfound.com/company/indiabizforsale-com/jobs</t>
+          <t>https://www.karza.in/careers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://lingarogroup.com/careers/india</t>
+          <t>https://www.idfy.com/careers/</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://jobs.sentinelassam.com/jobs-in-rest-of-india/jobs-in-india-intelligence-bureau-recruitment-2025-multi-tasking-staff-vacancy-10786999</t>
+          <t>https://jobs.bureau.id/</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://www.builtinnyc.com/company/zeta-global/jobs</t>
+          <t>https://www.zeta.tech/careers/</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://jobs.reczee.com/finbox</t>
+          <t>https://www.finbox.in/careers/</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://in.jobeka.com/jobs-senior-devops-engineer-hyderabad</t>
+          <t>https://go-yubi.zohorecruit.in/jobs/careers</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://cutshort.io/company/progcap-bXhtzcXj</t>
+          <t>https://www.progcap.com/careers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/Lendingkart/</t>
+          <t>https://www.lendingkart.com/careers/</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://www.shareindia.com/about-us/careers</t>
+          <t>https://www.axio.co.in/careers</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://www.ambitionbox.com/jobs/hdb-financial-services-jobs-cmp</t>
+          <t>https://www.neogrowth.in/careers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://www.ambitionbox.com/jobs/incred-finance-jobs-cmp</t>
+          <t>https://www.incredgroup.com/careers/</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://www.instahyre.com/jobs-at-fibe-india-2/</t>
+          <t>https://www.fibe.in/careers/</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://techwireasia.com/2021/08/can-ai-and-ml-help-reduce-fraud-detection-in-india/</t>
+          <t>https://www.stashfin.com/careers/</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://yourstory.com/2021/11/jobs-roundup-mumbai-drip-capital-cross-border-trade-finance</t>
+          <t>https://www.dripcapital.com/en-us/careers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://yourstory.com/2021/08/quotes-covid19-resilience</t>
+          <t>https://apply.workable.com/tradecred/</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://wellfound.com/company/niyo-sol</t>
+          <t>https://www.niyo.co/careers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://wellfound.com/company/vested-finance-1/jobs</t>
+          <t>https://vestedfinance.com/careers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://internshala.com/jobs/job-at-grip-invest/</t>
+          <t>https://grip.recruitee.com/</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://www.jobscity.net/pls/jobs/companyprofile2</t>
+          <t>https://www.wintwealth.com/careers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://jobs.accel.com/companies/jiraaf</t>
+          <t>https://www.jiraaf.com/careers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://internshala.com/jobs/job-at-tykevision-technologies-private-limited/</t>
+          <t>https://tykeinvest.com/careers</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://dribbble.com/jobs/81518-Lead-Product-Designer</t>
+          <t>https://www.khatabook.com/careers/</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/okcredit/jobs</t>
+          <t>https://okcredit.in/careers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/Vyaparin</t>
+          <t>https://www.vyaparapp.in/careers/</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://www.instahyre.com/jobs-at-mybillbook-flobiz/</t>
+          <t>https://mybillbook.in/careers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://wellfound.com/company/zestmoney/jobs</t>
+          <t>https://www.zestmoney.in/join-us/</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://ring.darwinbox.in/ms/candidate/careers</t>
+          <t>https://www.kissht.com/about/careers/</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://www.freshersworld.com/jobs/business-development-sales-jobs-in-across-india-axio-biosolutions-1876211</t>
+          <t>https://www.axio.co.in/careers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://www.instahyre.com/jobs-at-freo/</t>
+          <t>https://www.freo.money/careers/</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://cutshort.io/company/bankbazaarcom-trAyfKke</t>
+          <t>https://www.bankbazaar.com/careers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://cutshort.io/company/indialends-KkI5ikC4</t>
+          <t>https://www.indialends.com/careers</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://www.microsave.net/2019/07/15/kaarva-a-micro-salary-advance-for-a-micro-expense/</t>
+          <t>https://www.kaarva.com/careers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://finzly.com/careers/</t>
+          <t>https://careers.finzy.com/</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://jobs4fresher.com/lendenclub-off-campus-hiring-sep-2022/</t>
+          <t>https://careers.lendenclub.com/</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://blog.himanshusheth.net/2016/10/10/raghavendra-pratap-singh-i2ifunding/</t>
+          <t>https://www.i2ifunding.com/career/</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://internshala.com/jobs/job-at-monexo-fintech-private-limited/</t>
+          <t>https://www.monexo.co/career</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://confidential.careers/jobs/finance-jobs-in-mumbai</t>
+          <t>https://www.dezerv.in/careers/</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://www.instahyre.com/jobs-at-powerup-money/</t>
+          <t>https://www.powerupmoney.ai/careers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://www.uplers.com/company/taxbuddy-12065</t>
+          <t>https://www.taxbuddy.com/careers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://angel.co/company/quicko/jobs/1197075-ui-ux-designer</t>
+          <t>https://quicko.zohorecruit.in/jobs/Careers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://careers.chime.com/en/jobs/</t>
+          <t>https://www.chime.com/careers/</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://builtin.com/company/affirm/jobSearchUrl</t>
+          <t>https://www.affirm.com/careers/</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/Gusto2/</t>
+          <t>https://job-boards.greenhouse.io/gusto/jobs/6690251</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://datasciencejobs.com/jobs/senior-data-scientist-carta-united-states-2/</t>
+          <t>https://www.carta.com/careers/</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://www.themuse.com/jobs/fundbox/manager-credit-strategy</t>
+          <t>https://www.fundbox.com/careers/</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://www.talent.com/jobs/k-data-science-l-bellevue-wa</t>
+          <t>https://www.varomoney.com/careers/</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://moov.co/careers</t>
+          <t>https://moov.io/careers/</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://peacefulcareers.org/category/public-service-careers/</t>
+          <t>https://public.com/careers</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://pngset.com/free/careers</t>
+          <t>https://www.wealthfront.com/careers/</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://careers.adyen.com/press-and-media/adyen-and-billie-partner-up-to-bring-buy-now-pay-later-to-businesses-across-europe</t>
+          <t>https://careers.adyen.com/</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://www.revolut.com/careers/</t>
+          <t>https://www.revolut.com/careers</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://www.bayt.com/en/uae/jobs/jobs-in-dubai/</t>
+          <t>https://www.checkout.com/careers/</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/sumup/senior-online-marketing-manager-performance-europe-berlin-177067</t>
+          <t>https://www.sumup.com/careers/</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/mollie/90c64801-d5d9-4cf8-be64-832bd215d0d4</t>
+          <t>https://jobs.mollie.com/</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://www.glencore.com/careers/jobs</t>
+          <t>https://www.solarisgroup.com/careers/</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://jobs.thelocal.com/company/trade-republic-bank-gmbh/</t>
+          <t>https://www.traderepublic.com/careers/</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/bitpanda</t>
+          <t>https://www.bitpanda.com/en/career</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://www.foodnetwork.com/topics/raisins</t>
+          <t>https://www.raisin.com/en/corporate/careers/</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://www.jobfluent.com/company/zopa</t>
+          <t>https://careers.zopa.com/</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://empllo.com/company/monzo/jobs</t>
+          <t>https://www.monzo.com/careers/</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://www.fintechcareers.com/employer/truelayer/</t>
+          <t>https://careers.truelayer.com/</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://meetfrank.com/jobs/payhawk-3/senior-hr-business-partner</t>
+          <t>https://www.payhawk.com/careers/</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://jobs.eu.lever.co/pnlfin</t>
+          <t>https://careers.finom.co/</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://viralvybes.com/jobs-in-singapore-for-foreign-talent-2025-guide-to-high-demand-roles-with-visa-sponsorship/</t>
+          <t>https://www.grab.com/careers/</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://digitalmarketingjobs.com/jobs/in-singapore-central-singapore</t>
+          <t>https://careers.syfe.com/</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://careersatsea.bs-shipmanagement.com/IdentityServer/Seafarer</t>
+          <t>https://hire-r1.mokahr.com/su/f4aa3</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://validus.vn/en/jobs/relationship-manager-2/</t>
+          <t>https://apply.workable.com/validus-risk-management/j/F13B7F4D8B/</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://careersatsea.bs-shipmanagement.com/IdentityServer/Seafarer</t>
+          <t>https://www.tonikbank.com/careers/</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/MATCHMOVEPAY</t>
+          <t>https://www.matchmove.com/careers</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://careersatsea.bs-shipmanagement.com/IdentityServer/Seafarer</t>
+          <t>https://you.co/careers/</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://www.efinancialcareers.sg/jobs-Singapore-Singapore-Card_Strategy_and_Operations_Manager_-_Instarem.id21368846</t>
+          <t>https://www.instarem.com/careers/</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://www.careers24.com/jobs/kw-production-manager-chocolate-candy-mbombela/</t>
+          <t>https://www.chocolatefinance.com/</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://jobs.laimoon.com/ar/saudi/government</t>
+          <t>https://careers.tabby.ai/</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://www.oracle.com/middleeast/careers/</t>
+          <t>https://www.tamara.co/careers/</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://www.bayt.com/en/international/jobs/</t>
+          <t>https://apply.workable.com/yap-global/</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://www.workforceaustralia.gov.au/individuals/jobs</t>
+          <t>https://careers.sarwa.co/</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://wuzzuf.net/jobs/p/6lewUQZnEsfB-Junior-Marketing-Specialist-IFTC-Middle-East-Giza-Egypt</t>
+          <t>https://getbaraka.com/careers</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://careers.aggreko.com/middle-east/en</t>
+          <t>https://www.beehive.net/careers/</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://www.flexxpay.com/en</t>
+          <t>https://www.flexxpay.com/careers</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://paytabs.hire.trakstar.com/jobs</t>
+          <t>https://ai.paytabs.com/en/career/</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://careers.aggreko.com/middle-east/en</t>
+          <t>https://www.telr.com/careers</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/Mamo</t>
+          <t>https://www.mamopay.com/careers/</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://www.alaan.com/careers</t>
+          <t>https://www.nymcard.com/careers/</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://builtin.com/company/finverity/jobs</t>
+          <t>https://www.finverity.com/careers</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/companies/ziina/jobs/WRU4wzI-senior-backend-engineer</t>
+          <t>https://www.ziina.com/careers/</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">

--- a/fintech_companies_structured.xlsx
+++ b/fintech_companies_structured.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F193"/>
+  <dimension ref="A1:F347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://www.axio.co.in/careers</t>
+          <t>https://www.getwalnut.com/careers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/walnut-india/jobs/</t>
+          <t>https://www.linkedin.com/company/walnutapp/jobs/</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://cube.global/about-us/careers/</t>
+          <t>https://www.bankoncube.com/careers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6589,6 +6589,4934 @@
       <c r="F193" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/ziina/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>1Crowd</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://login.1crowd.co/entrepreneur/index.php/about_us</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/1crowd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>5paisa Capital</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://www.5paisa.com/careers/</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/5paisa/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Advarisk</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://www.advarisk.com/careers/</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/advarra/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Advisorymandi.com</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://www.advisorymandi.com/careers</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/advisory-mandi/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Affordplan</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://www.affordplan.com/careers/</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/affordplan/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Agrim</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://agrim.zohorecruit.in/jobs/Careers</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/agrimindia/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Agrosperity Tech Solutions</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://www.agrotechsolns.com/</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kivi-agrosperity/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Arthmate</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://www.arthmate.com/careers/</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/arthmate/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Ascend Capital</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://www.inclusivecapitalism.com/careers/</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ascendcap/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Assurekit</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://assurekit.com/blog/busting-common-myths-about-insurance</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/assurekit/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Autovert</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://www.autovert.com/careers</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/autovert-technologies-pvt-ltd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Auxilo</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://www.auxilo.com/careers/</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/auxilo/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Avanti</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://apply.workable.com/avantilearning/</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/avanti/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Basic Home Loan</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://www.basichomeloan.com/careers/</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/basichomeloan/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Bimaplan</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://www.bimaplan.com/careers</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bimaplan/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>BonusHub</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://bonushub.co.in/BHCareer.aspx</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bonushub-digital-solutions/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Card91</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://www.card91.io/careers/</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/card91/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Cashflo</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://www.cashflo.io/about/careers/</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cashfloio/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Chqbook</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://www.chqbook.com/careers</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/chqbook/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Clix Capital</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://www.clix.capital/careers/</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/clix-capital/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>CredAble</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://www.credable.biz/careers/</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/credable.in/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Credgenics</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://www.credgenics.com/terms-of-use</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/credgenics/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Credilio</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://w3.credilio.in/careers/</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/credilio/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Credit Fair</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://www.trueandfair.pro/Careers</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/credit-fair/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>CreditNirvana</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://www.creditnirvana.ai/careers/</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/credit-nirvana/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>CrediWatch</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://about.crediwatch.com/about/careers/</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/crediwatch/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Credochain</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://www.credochain.com/careers</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/credochain-technologies-pvt-ltd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>CredRight</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://credright.zohorecruit.in/jobs/Career-Site</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/credright-pvt-ltd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Credy</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://careers.cred.club/</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cready.in/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Davinta</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://www.davintafinserv.com/career.php</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/davintafinserv/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>DGV</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://www.dgv.com/careers</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/neobharatbanking/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Digio</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://www.digioleathersofa.com/privacy-policy/</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/digio.in/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Drona Pay</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://www.dronapay.com/careers/</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/drona-pay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Ecofy</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://www.ecofy.co.in/careers/</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ecofy/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Eduvanz</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://www.eduvanz.com/careers/</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/eduvanz/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>EHFL</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>http://www.ehfl.in/</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/easyhomefinance/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Enterprise Tiger</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>https://www.tigerdata.com/careers</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sumeru-enterprise-tiger-business-solutions-pvt.ltd./jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>ePayLater</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://www.epaylater.in/careers.html</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/epaylater/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Esthenos</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>https://www.esthenos.com/</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/esthenos-technologies-pvt-limited/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>EximPe</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>https://www.eximpe.com/careers</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/eximpe/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>FamApp</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://www.famapp.in/careers/</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/famappbytrio/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Fello</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>https://fello.in/careers/</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fello-ai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Fi</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/fi/</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fi-india/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Fibe</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>https://www.fibe.in/careers/</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fibe-in/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>FidyPay</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>https://www.fidypay.com/careers</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jpe-fidypay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>FinAGG</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>https://www.finagg.in/career</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/finagg-technologies-private-limited/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Finbingo</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>https://www.finbingo.com/careers</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/finbingo/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>FinBit</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>https://finbite.eu/en/job-offers/</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/finbit-io/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>FingPay</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>https://www.fingpay.co.in/jobs/</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fingpay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Finity</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>https://www.thefinitygroup.com/careers/</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/finity-official/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Finnable</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>https://www.finnable.com/about-us/</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/finnable-credit-pvt-ltd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Fisdom</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>https://www.fisdom.com/careers/</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fisdom/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Flexmoney</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>https://www.flexmoney.com/careers</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/flexmoney-technologies-pvt-ltd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Ftcash</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>https://www.ftcash.com/careers</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ftcash/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>GetVantage</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>https://www.getvantage.com/careers</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/getvantage/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>GramCover</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>https://www.gramcover.com/careers</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gramcover/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>GrayQuest</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>https://www.grayquest.com/careers</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/grayquest/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Grip</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>https://www.gripworks.com/careers/</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gripinvest/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>GroMo</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>https://careers.gromo.in/</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gromofintech/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>GyanDhan</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>https://www.gyandhan.com/aboutus</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gyandhan/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Happy Loans</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>https://www.happymoney.com/careers/</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/olyv-india/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>HomeCapital</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>https://blog.homecapital.in/careers/</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/homecapital/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>indiagold</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>https://www.indiagold.net/careers/</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/indiagold/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>InsuranceDekho</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>https://careers.insurancedekho.com/</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/insurancedekho/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>InvestorAi</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>https://www.investorai.in/</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/investor-ai/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Jai Kisan</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>https://www.jaihokisan.in/joinour-team.html</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jai-kisan/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Jama Wealth</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>https://wealthindia.keka.com/careers/articles-jobs</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maxiomwealth/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>https://myjar.app/careers</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jarapp/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Jodo</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>https://www.jodo.in/careers/</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jodo-india-social-foundation/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Kaleidofin</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>https://www.kaleidofin.com/careers/</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kaleidofin/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>KapitalTech</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>https://www.kapitaltech.com/careers</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kapitaltech/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Kinara Capital</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>https://kinara.co/job-board/</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kinaracapital/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Kiwi</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>https://www.kiwitech.com/careers</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gokiwinow/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>KNAB Finance</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>https://www.werkenbijknab.nl/en/finance</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/knab/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Kosh</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>https://oshkoshcorporation.wd5.myworkdayjobs.com/Oshkosh</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/getkosh/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>KredX</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>https://www.kredx.com/careers/</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kredxindia/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>LEO 1</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>https://www.leo1.com/careers</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/leo1/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>LiquiLoans</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>https://www.liquiloans.com/careers/</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/liquiloans/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>LivFin</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>https://www.livfin.com/careers</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/livfin/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Loan Frame</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>https://www.loanframe.com/careers/</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/loan-frame/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>M1xchange</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>https://www.m1xchange.com/jobs/</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mynd-online-national-exchange/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>M2P</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>https://www.m2p.net/us/careers/working-at-m2p</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m2pfintech/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>MarketsMojo</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>https://www.marketsmojo.com/mojo/career</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/marketsmojoconnect/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>MarketWolf</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>https://www.marketwolf.com/careers</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/marketwolf/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Minko</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>https://www.minkoaisystems.com.ng/careers/</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/minko/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Mintifi</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>https://www.mintifi.com/careers</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mintifi/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Mintoak</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>https://www.mintoak.com/contact-us</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mintoak-innovations-private-limited/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Modefin</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>https://www.modefin.com/careers/</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/modefin/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Monedo</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>https://www.monedo.in/careers/</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/monedofinancial/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>MyLoanCare</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>https://www.myloancare.com/careers</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/moneywidemw/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>MyShubhLife</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>https://www.myshubhlife.com/careers.html</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/myshubhlife/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Namaste Credit</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>https://www.smfgindiacredit.com/careers/</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/namaste-credit/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>New Street Tech</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>https://www.st.com/content/st_com/en/about/careers.html</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/newstreettech/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>New Street Technologies</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>https://www.jobstreet.com/</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/newstreettech/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>NIRA</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>https://www.nirafinance.com/careers/</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nirafinance/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Nira Finance</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>https://www.nirafinance.com/careers/</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nirafinance/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Niro</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>https://nirowealth.com/careers/</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/niromoney/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Niyogin</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>https://www.niyogin.com/careers/</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/niyogin.in/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Nova Benefits</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>https://www.novabenefits.com/careers/</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nova-benefits/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>NPST</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>https://www.npstx.com/careers/</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/npstx/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>OLA Money</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>https://www.olamoney.com/careers</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/olacabs-com/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Olyv</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>https://www.olyv.co.in/jobs/</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/olyv-india/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Onebanc</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>https://www.onebanc.ai/careers/</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/onebanc/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Onemoney</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>https://www.onemoney.in/careers.html</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/onemoney/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>OneStack</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>https://onestackhq.com/careers</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/onestack-india/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>OnSurity</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>https://www.onsurity.com/careers/</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/onsurity/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Oro Money</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>https://www.oromoney.in/careers/</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/orocorp/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Orocorp Technologies</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>https://www.orocorp.in/</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/orocorp/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>OTO</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>https://apply.workable.com/oto/</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/oto-india/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>PayGlocal</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>https://www.payglocal.com/careers/</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/payglocal/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>PayMeIndia</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>https://payme.io/careers/</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/payme-india-ltd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>PayPhi</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>https://phi.co.in/careers/</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/phicommerce/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Paytm Money</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>https://www.paytm.com/careers/</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/paytmmoney/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Paz Care</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>https://www.pazcare.com/careers-at-pazcare</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/paz-care/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Phocket</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>https://www.phocket.co.in/</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/phocket-instant-access-to-cash/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Plum</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>https://www.plumgoodness.com/careers/</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/plum-goodness/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Propelld</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>https://www.propelld.com/careers/</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/propelld/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>PropertyShare</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>https://propertyshares.com.au/aboutus</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/propertyshare/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>psbloansin59minutes.com</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>https://www.psbloansin59minutes.com/careers</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/psbloansin59minutes/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>QuickInsure</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>https://quickinsureindia.blogspot.com/2024/06/start-your-career-as-insurancepos-agent.html</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/quickinsure/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Raise</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>https://www.raiselp.com/careers/</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/raise-india-ngo/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>RevFin</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>https://revfin.in/career</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/revfinindia/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Riskcovry</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>https://www.riskcovry.com/careers</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/riskcovrycom/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>RupeeRedee</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>https://www.rupeeredee.com/careers</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rupeeredee/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Rupifi</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>https://www.rupifi.com/careers</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rupifi/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>SabPaisa</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>https://careers.sabpaisa.in/</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sabpaisa/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>SafexPay</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>https://www.safexpay.com/careers</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fintechcompanyltd/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Scoreme</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>https://www.scoreme.in/jobs/</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/scoremesolutions/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>SecureNow</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>https://www.securenow.in/careers/</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/securenow-insurance-broker/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>ShopSe</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>https://www.getshopse.com/career</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/shopse/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Siply</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>https://www.siply.com/careers</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/siply-india/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Strata</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>https://www.strataglobal.com/careers/</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/strata-geosystems/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>SuperMoney</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>https://www.supermoney.com/careers</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/supermoneyindia/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Symbo</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>https://www.symbo.co/careers</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/symbo-global/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Symbo Insurance</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>https://www.symbo.co/careers</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/symbo-global/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Synaptic</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>https://www.synaptics.com/careers/</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/synaptics/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>TCPL</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>https://www.tcplquincy.org/jobs/</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tcpl-packaging-limited/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Toffee</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>http://www.mwtoffee.com/Careers</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/toffeecoffeeroasters/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>ToneTag</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>https://www.tonetag.com/careers</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tonetag/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Trustt</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>https://www.trustt.com/careers/</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/trustt-tribe/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>TWID</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>https://www.twid.com/careers</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/twidpay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>UBFC</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>https://www.ubfc.fr/en/ubfc/human-resources/recruitment/ubfc-recruitment/</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unnayan-bharat-finance-corporation-private-limited/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Unnati</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>https://unnati-isec.org/careers.html</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unnati/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Upswing</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>https://upswing.io/careers/</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/upswing-financial-technologies/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Veefin</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>https://veefin.com/careers.php</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/veefin/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>VegaPay</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>https://www.vegapay.tech/careers</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vegapay/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>https://www.velocitytruckcenters.com/careers</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/velocity-in/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Vitraya</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>https://vitraya.com/career</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vitrayatech/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Vivifi India Finance</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>https://www.vivifin.com/careers</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vivifi-india/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Vivriti Capital</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>https://www.vivritiamc.com/careers</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vivriti-capital/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>WealthDesk</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>https://www.wealthdesk.com/careers</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wealth-technology-and-services-pvt.-ltd./jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Wealthy</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>https://www.wealthy.in/careers/</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wealthy-in/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>WeRize</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>https://werize.snaphunt.com/</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/werize/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>WonderLend Hubs</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>BFSI FinTech list 2025</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>https://www.wonderlendhubs.com/careers</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wonderlend-hubs/jobs/</t>
         </is>
       </c>
     </row>

--- a/fintech_companies_structured.xlsx
+++ b/fintech_companies_structured.xlsx
@@ -10197,11 +10197,7 @@
           <t>BFSI FinTech list 2025</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>https://www.paytm.com/careers/</t>
-        </is>
-      </c>
+      <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/paytmmoney/jobs/</t>
